--- a/results/base-v1/MANDATORY_STRESS/export.xlsx
+++ b/results/base-v1/MANDATORY_STRESS/export.xlsx
@@ -183,7 +183,593 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">risk_id</t>
+          <t xml:space="preserve">base_scenario</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cause</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">data_dir</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dependencies</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">event</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">likelihood</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">measure</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">owner</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameters</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">period</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">plan_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">plan_patch</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scenario_id</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BASE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Правило ввода 18-24 месяца после исполнения опциона: срок подготовки может выйти за верхнюю границу окна</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">["опцион 2035, исполнение 2036", "заказы Core на 2038 уже размещены (январь 2037)"]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Канал Earth-New не даёт поставок в 2038, работает с 2039</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">интервал 18-24 месяца задан кейсом, вероятность выхода за 24 не задана; риск считается существенным, потому что план берёт 90 т у нового канала в первый год</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"title": "Бронь Flex 110 т на 2038 в базовом плане, заказ 105 т при подтверждении задержки (до сентября 2037)", "prep": {"reservations": {"B": {"2038": 110}}}, "response": {"orders": {"B": {"2038": 105}}}, "note": "Бронь платится всегда (0,15 млн за тонну в год), заказ - только при задержке. Ход строительства виден к середине 2037, срок заказа Flex 4 месяца."}</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">поставщик Earth-New; оператор узла отвечает за резервный заказ</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">["поставка Earth-New 2038: 90 т -&gt; 0", "запас на 1 января 2039", "закупка у Flex по 8,9 вместо 7,1"]</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2038</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEAM_EARTH_NEW_DELAY</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ввод Earth-New задерживается на год</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BASE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Отказ носителя или задержка кампании; reliability 0,96 в данных говорит о возможности, но не о распределении</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">["Core на пределе мощности с 2037, заменить объём в том же году может только Flex или Emergency"]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Основной канал привозит 90 % заказа в 2039</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">интервал: один плохой год на горизонте с недопоставкой 5-10 %; берём 10 % как верхнюю границу</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"title": "Бронь Emergency 20 т на 2039, заказ по факту недопоставки (срок 6 недель)", "prep": {"reservations": {"E": {"2039": 20}}}, "response": {"orders": {"E": {"2039": 20}}}, "note": "Недопоставка видна по графику кампании внутри года, Emergency успевает за 6 недель."}</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">поставщик Earth-Core; оператор узла</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">["поставка Core 2039: 190 -&gt; 171 т", "запас на 1 января 2040"]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2039</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEAM_CORE_SHORT</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Недопоставка Earth-Core в один год</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BASE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Больше миссий и коммерческих заправок, чем в базовом прогнозе</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">["Core и Earth-New на пределе мощности, добавить можно только Flex (110 т) и Emergency (80 т)"]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Спрос идёт по верхней траектории организаторов: +10 % в 2035-2037, +25 % в 2038-2040</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">high_total_t дан организаторами как контрольная точка; отклонение +10 % видно уже по 2035-2036, что даёт время на заказы</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"title": "Flex 25 т уже в 2035, брони Flex 40-110 т на 2036-2040 и Emergency 20 и 60 т на 2039-2040 в базовом плане, заказы по фактическому спросу", "prep": {"orders": {"B": {"2035": 25}}, "reservations": {"B": {"2035": 25, "2036": 60, "2037": 40, "2038": 60, "2039": 110, "2040": 110}, "E": {"2039": 20, "2040": 60}}}, "response": {"orders": {"B": {"2036": 50, "2037": 25, "2038": 50, "2039": 110, "2040": 110}, "E": {"2039": 20, "2040": 50}}}, "note": "Заказ Flex на 2035 в модели размещается до начала горизонта, поэтому лишние 10 т на 2035 входят в базовый план как страховка: 30 т уже переполняют бак в 2036 стандартного сценария. Отклонение +10 % видно по 2035, заказ Flex на 2036 размещается до сентября 2035, дальше заказы идут по факту спроса. В 2039-2040 Flex на пределе 110 т, добор через Emergency."}</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">оператор узла и потребители; финансирующая сторона по дополнительным закупкам</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">["спрос по годам", "запас и резерв 45 дней", "закупка у Flex"]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2035-2040, критично с 2038</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Спрос выше базового прогноза</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BASE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ограничения на пусковые услуги, рост цен на носители</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">["брони и take-or-pay по условиям кейса не индексируются"]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Переменная цена Core и Flex +50 %, Earth-New и Emergency +30 % в 2038-2040</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R4</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">диапазон: обязательный стресс даёт +25 % на два года, здесь +50 % на три года как верхняя граница; вероятность не оценивается</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"title": "Мер в плане заказов нет: физический баланс не страдает, растёт только стоимость. Фиксация цены в контракте вне модели; стратегическая страховка - вариант v3-lunar", "prep": null, "response": null, "note": "Остаток равен эффекту. Страховка вне модели заказов: вариант v3-lunar. При этом шоке он стоит 10 006 против 10 533 PV, но платит 1 430 CAPEX, 40 PV в стандартном сценарии и 436 PV в обязательном стрессе с ответом (docs/STRESS_RESPONSE.md, раздел 5)."}</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">финансирующая сторона; оператор узла по контрактам</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">["закупка", "PV"]</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2038-2040</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEAM_GEO_PRICE</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Геополитический рост цен земных каналов</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BASE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Задержка финансирования или поставки оборудования модернизации</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">["заказы Core и Earth-New на 2038 размещены в январе 2037 под ёмкость 120 т"]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZBO оплачена и введена в 2038 вместо 2037</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZBO доступна с 2036 по условиям кейса; сдвиг на год - обычный интервал для такого проекта, вероятность не задана</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"title": "Оплатить ZBO в 2036, на год раньше плана: запас по сроку", "prep": {"investments": {"ZBO": {"year": 2036}}}, "response": {"investments": {"ZBO": {"year": 2037}}}, "note": "Цена меры - более ранний CAPEX 180 и лишний год OPEX 12. Если ввод всё равно сдвигается на год, он попадает в 2037 и план цел."}</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">оператор узла; финансирующая сторона</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">["ёмкость бака 70 вместо 120 т в 2037-2038", "потери 4,5 % вместо 1,2 %", "переполнение"]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2037-2038</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"investments": {"ZBO": {"year": 2038}}}</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BASE</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оплата и ввод ZBO сдвигаются на год</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Коэффициент 1,2 % в кейсе синтетический, реальные криогенные потери не доказаны (SCIENTIFIC_BASIS.md)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">data_ext/loss_2pct</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">["ограничение STRESS_LOSS_LIMIT считается по отношению потерь к поступлению"]</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фактические потери ZBO 2,0 % от поступления вместо 1,2 %</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">интервал 1,2-2,0 %; основание - оговорка организаторов о неуниверсальности коэффициента</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"title": "Мер в модели нет: потолок потерь задан на уровне 2 %, при 2,0 % план на границе. Инженерная мера - приёмочные испытания ZBO до 2038", "prep": null, "response": null, "note": "Считается на копии данных data_ext/loss_2pct. Показывает, что ограничение организаторов продолжает действовать на копии."}</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">поставщик ZBO; оператор узла</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">["потери", "запас", "потолок потерь 2 % в стрессе с 2038"]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2037-2040</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v3-earth-response</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Потери ZBO выше паспортных</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В стрессе гибкую мощность разбирают все операторы</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">["ответ на стресс v3-earth-response опирается на Flex 75 и 70 т"]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Обязательный стресс, и Earth-Flex привозит 80 % заказа в 2039-2040</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">порог 80 % найден анализом чувствительности; вероятность не задана, шок комбинированный и объявлен явно</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"title": "Бронь Emergency 40 т на 2039-2040 в ответе на стресс, заказ при недопоставке Flex", "prep": {"reservations": {"E": {"2039": 40, "2040": 40}}}, "response": {"orders": {"E": {"2039": 30, "2040": 40}}}, "note": "Бронь Emergency на 2039 размещается до ноября 2038, уже после начала стресса."}</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">оператор узла; поставщик Flex</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">["поставка Flex", "запас на 1 января 2040", "резерв 45 дней"]</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2039-2040</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v3-earth-response</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEAM_FLEX_SQUEEZE</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В стрессе не хватает гибкой мощности</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BASE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Меньше миссий; узел законтрактовал Core на пределе с take-or-pay 70 %</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">["заказы Core размещаются за 12 месяцев, брони Core - под take-or-pay 70 %"]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Спрос по нижней траектории организаторов: -20 % каждый год</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low_total_t дан организаторами; отклонение -20 % видно по 2035, время на снижение заказов есть</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"title": "Снизить заказы Core и Earth-New с 2037 под фактический спрос, брони оставить", "prep": null, "response": {"orders": {"A": {"2036": 115, "2037": 150, "2038": 150, "2039": 150, "2040": 155}, "B": {"2036": 20, "2038": 0, "2039": 0, "2040": 0}, "C": {"2038": 60, "2039": 90, "2040": 115}}}, "note": "Брони не меняются: Core забирают 820 т из 990, брони оплачены целиком, take-or-pay не срабатывает (70 % от 990 = 693 т). Остаточная цена контракта при низком спросе - плата за незабранную бронь."}</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">оператор узла; финансирующая сторона несёт take-or-pay</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">["переполнение бака", "take-or-pay за незабранный объём", "затраты на тонну"]</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2035-2040</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Спрос ниже прогноза: переполнение и take-or-pay</t>
         </is>
       </c>
     </row>
